--- a/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>聲波遇障礙反射形成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>回聲</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>共鳴</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>阻隔噪音傳播</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>頻率相同引發振幅加大稱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>共振/共鳴</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>反射成像</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>能量集中方向</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>能量傳遞</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>頻率超過20000Hz的聲波是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>放大聲音</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>反射成像</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>超聲波</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>超音波</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>聽不到</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>聲納利用什麼原理？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>回聲測距</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>能量集中方向</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>醫學上看胎兒常用？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>聽力</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>超音波</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>分貝dB</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>超聲波</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>長期噪音會損害？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>共振/共鳴</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>聽力</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>回聲測距</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>健康危害</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>樂器的共鳴箱作用是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>能量集中方向</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>放大聲音</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>共振/共鳴</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>共鳴</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>噪音大小用什麼衡量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>分貝dB</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>放大聲音</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>回聲測距</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>響度</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>超聲波是人耳聽得到還聽不到？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>反射成像</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>聽不到</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>鋪設吸音材料</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>超過可聽域</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>回聲是聲音的什麼現象？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>共振/共鳴</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>回聲1秒後聽到(340m/s)障礙距離？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>頻率高指向性佳、可測細微</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>170 m</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>外力頻率與固有頻率相同振幅劇增</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>被動監聽不主動發聲</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>340×1÷2</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>倒車雷達用什麼波？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>聽力</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>超聲波</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>測距</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>音叉A振動使旁邊同頻音叉B也響是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>放大聲音</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>聽力</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>共鳴</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>頻率相同</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>超聲波指向性佳的意思？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>共鳴</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>能量集中方向</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>較準</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>隔音牆的功能是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>阻隔噪音傳播</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>共振/共鳴</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>聽力</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>防治</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>聲納測水深來回3秒(1500m/s)？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>2250 m</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>聲來回走兩倍距離</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>障礙夠遠時間差足夠分辨</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>1500×3÷2</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>超聲波清洗利用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>高頻振動震落污垢</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>被動監聽不主動發聲</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>頻率高指向性佳、可測細微</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>障礙夠遠時間差足夠分辨</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>回聲需距障礙夠遠才聽得清因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>超音波</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>時間差要足夠</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>放大聲音</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>超聲波</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>分辨</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>醫院超音波檢查利用超聲波的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>阻隔噪音傳播</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>反射成像</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>超音波</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>回聲0.5秒後聽到(340)障礙距離？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>85 m</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>時間差要足夠</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2250 m</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>340×0.5÷2</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上3-4 聲音的現象與應用　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何共振可能造成橋樑危險？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>聲來回走兩倍距離</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>外力頻率與固有頻率相同振幅劇增</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>使更多空氣振動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>障礙夠遠時間差足夠分辨</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>工程警示</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>超聲波比可聽聲優在哪？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>聲來回走兩倍距離</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>發超聲波聽回聲定位</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>頻率高指向性佳、可測細微</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>障礙夠遠時間差足夠分辨</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>回聲測距為何要除以2？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>量化響度以便規範</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>使更多空氣振動</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>聲來回走兩倍距離</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>外力頻率與固有頻率相同振幅劇增</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>往返</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>如何降低室內回音？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>放大聲音</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>鋪設吸音材料</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>超音波</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>吸音</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>軍艦怎麼用聲納避免被發現？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>發超聲波聽回聲定位</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>被動監聽不主動發聲</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>高頻振動震落污垢</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>聲來回走兩倍距離</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>戰術</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>共鳴箱不放大能量卻讓聲更大因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>高頻振動震落污垢</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>發超聲波聽回聲定位</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>使更多空氣振動</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>頻率高指向性佳、可測細微</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>傳遞效率</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>噪音管制為何用分貝分級？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>量化響度以便規範</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>聲來回走兩倍距離</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>清洗與工業檢測</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>外力頻率與固有頻率相同振幅劇增</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>標準</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>蝙蝠如何在暗中飛行？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>高頻振動震落污垢</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>發超聲波聽回聲定位</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>被動監聽不主動發聲</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>清洗與工業檢測</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>回聲定位</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何空曠山谷易聽到回聲？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>高頻振動震落污垢</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>障礙夠遠時間差足夠分辨</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>被動監聽不主動發聲</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>量化響度以便規範</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>分辨</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>超聲波除測距與醫學外的應用？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>清洗與工業檢測</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>量化響度以便規範</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>障礙夠遠時間差足夠分辨</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>外力頻率與固有頻率相同振幅劇增</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：聲波遇到障礙物反彈回來、再次被聽到的現象稱為回聲，是聲音的反射</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>能量傳遞</t>
+          <t>能量傳遞：當外力振動的頻率和物體本身的固有頻率相同時，會把能量有效傳給物體，使物體振幅大幅增加，這種現象叫共振或共鳴</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>聽不到：頻率高於20000赫茲的聲波稱為超聲波，超出人耳可聽範圍，人耳聽不到</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：聲納發出聲波，遇到物體反射回來，靠測量來回時間換算出距離，原理是聲音的反射</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>超聲波：醫學上常利用超聲波(超音波)不傷害人體組織、又能反射成像的特性，來觀察胎兒或體內器官</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>健康危害</t>
+          <t>健康危害：長期暴露在噪音環境中，會使耳朵內的聽覺構造受損，造成聽力下降甚至失聰</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>共鳴</t>
+          <t>共鳴：樂器的共鳴箱能與弦或簧片的振動產生共鳴，使更多空氣一起振動，讓聲音聽起來更大、更飽滿</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>響度</t>
+          <t>響度：噪音的大小聲(響度)常用分貝(dB)這個單位來衡量</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>超過可聽域</t>
+          <t>超過可聽域：超聲波的頻率超過人耳能聽到的範圍(可聽域)，所以人耳聽不到超聲波</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：聲波遇到障礙物反彈回來、再次被聽到的現象稱為回聲，屬於聲音的反射</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>340×1÷2</t>
+          <t>340×1÷2：聲音來回共花1秒，單程距離=波速×時間÷2，340乘以1再除以2等於170公尺</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>測距</t>
+          <t>測距：倒車雷達發射超聲波，利用碰到障礙物反射回來所需的時間來計算距離</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>頻率相同</t>
+          <t>頻率相同：音叉B的固有頻率和音叉A振動的頻率相同，A傳來的聲波能有效把能量傳給B，引發B共鳴發聲</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>較準</t>
+          <t>較準：超聲波波長短，傳播時能量比較集中在特定方向前進、不容易散開，這種特性稱為指向性佳，適合精確測距</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>防治</t>
+          <t>防治：隔音牆能阻擋或吸收聲波，減少噪音從一處傳到另一處，是噪音防治的常見措施</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>1500×3÷2</t>
+          <t>1500×3÷2：聲音在水中來回共花3秒，單程距離=波速×時間÷2，1500乘以3再除以2等於2250公尺</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：超聲波清洗機利用超聲波產生的高頻振動，使清洗液產生微小氣泡衝擊物體表面，把污垢震落</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>分辨</t>
+          <t>分辨：聲音來回所需的時間差要夠大，人耳才能把回聲和原音分辨開來，如果障礙物太近，回聲和原音會混在一起聽不清楚</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：超音波檢查利用超聲波遇到體內不同組織會產生不同反射的特性，把反射訊號轉換成影像，用來觀察體內構造</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>340×0.5÷2</t>
+          <t>340×0.5÷2：聲音來回共花0.5秒，單程距離=波速×時間÷2，340乘以0.5再除以2等於85公尺</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>工程警示</t>
+          <t>工程警示：如果外力(例如風或人群踏步)振動的頻率剛好和橋樑本身的固有頻率相同，會引發共振，使橋樑振幅劇烈增大，可能導致結構損壞甚至倒塌，工程上要特別避免</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：超聲波頻率高、波長短，傳播時方向性好(指向性佳)，還能偵測到比較細微的構造變化，這些特性是一般可聽聲做不到的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>往返</t>
+          <t>往返：聲音從發出到碰到障礙物反射回來，實際上走了「去程+回程」兩倍的距離，所以要先算出來回的總距離，再除以2才是單程的真正距離</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>吸音</t>
+          <t>吸音：在牆面或天花板鋪設能吸收聲波能量的吸音材料，可以減少聲波反射，降低室內回音</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>戰術</t>
+          <t>戰術：軍艦可以改用被動聲納，只接收監聽周圍的聲音而不主動發出聲波，避免自己發出的聲波被敵方偵測到而暴露位置</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傳遞效率</t>
+          <t>傳遞效率：共鳴箱本身不會產生新的能量，但能讓更大範圍的空氣跟著一起振動，把原本分散微弱的振動能量更有效率地傳遞出去，聽起來就比較大聲</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>標準</t>
+          <t>標準：分貝能把聲音的大小聲用具體數字表示出來，方便訂定客觀的噪音管制標準，作為執法和規範的依據</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>回聲定位</t>
+          <t>回聲定位：蝙蝠會發出人耳聽不到的超聲波，靠聽取碰到物體反射回來的回聲，判斷障礙物的位置和距離，這種方式稱為回聲定位</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>分辨</t>
+          <t>分辨：山谷夠空曠、障礙物(對面山壁)距離夠遠，聲音來回所需的時間差夠大，人耳才能把回聲和原音分辨開來，聽起來才會是清楚的回聲，而不是混在一起</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：超聲波還可以應用在超音波清洗機(利用振動震落污垢)，以及工業上檢測金屬內部是否有裂痕瑕疵等領域</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-4_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>超音波</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>共鳴</t>
+          <t>反射成像</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阻隔噪音傳播</t>
+          <t>共振/共鳴</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>回聲</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>反射成像</t>
+          <t>反射</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>能量集中方向</t>
+          <t>聽力</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>時間差要足夠</t>
+          <t>聽力</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>反射成像</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>能量集中方向</t>
+          <t>分貝dB</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>聽不到</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>共振/共鳴</t>
+          <t>放大聲音</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>時間差要足夠</t>
+          <t>能量集中方向</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>頻率高指向性佳、可測細微</t>
+          <t>阻隔噪音傳播</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>外力頻率與固有頻率相同振幅劇增</t>
+          <t>回聲測距</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>被動監聽不主動發聲</t>
+          <t>時間差要足夠</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>超音波</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>回聲測距</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>放大聲音</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>聽力</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>回聲</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>聲來回走兩倍距離</t>
+          <t>能量集中方向</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>障礙夠遠時間差足夠分辨</t>
+          <t>阻隔噪音傳播</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>超聲波</t>
+          <t>共振/共鳴</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>阻隔噪音傳播</t>
+          <t>時間差要足夠</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>回聲</t>
+          <t>共鳴</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>時間差要足夠</t>
+          <t>放大聲音</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>回聲</t>
+          <t>共振/共鳴</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>2250 m</t>
+          <t>分貝dB</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
